--- a/data/Rival_Jam_table.xlsx
+++ b/data/Rival_Jam_table.xlsx
@@ -15,9 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Aptos Narrow"/>
@@ -447,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -516,8 +514,10 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>8603</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8603</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 666</t>
+          <t>666</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 303</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 303</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 303</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5674,6 +5674,1182 @@
       </c>
       <c r="L124" s="1" t="n">
         <v>45964</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L125" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L126" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>3</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>6</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L127" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L128" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L129" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>6</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>7</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L130" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>7</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>12</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L131" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>8</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>13</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L132" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>9</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L133" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L134" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>12</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L135" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>12</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>8</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L136" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>13</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L137" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>14</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>12</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L138" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L139" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>7</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L140" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>3</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>17</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L141" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L142" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>7</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L143" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>6</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L144" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>7</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L145" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L146" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>9</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>4</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L147" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>10</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L148" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>11</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>2</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L149" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>12</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>2</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L150" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>13</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>11</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L151" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>14</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>4</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="L152" s="1" t="n">
+        <v>46242</v>
       </c>
     </row>
   </sheetData>
